--- a/data/Change_log.xlsx
+++ b/data/Change_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/WP2.2.5_Data_Analysis/Sancho-SalasEtAl_Dataset_2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/Sancho-SalasEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E5840A-9398-A64B-82BF-A73681E538F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56137A76-5621-4047-9B2C-2C8E0C0BC4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9540" yWindow="8420" windowWidth="23080" windowHeight="12880" xr2:uid="{85E342D6-DF1C-2748-8694-49E262E0E776}"/>
+    <workbookView xWindow="33420" yWindow="29480" windowWidth="28320" windowHeight="21560" xr2:uid="{85E342D6-DF1C-2748-8694-49E262E0E776}"/>
   </bookViews>
   <sheets>
     <sheet name="example" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -129,13 +129,256 @@
   </si>
   <si>
     <t>7/19/2025 11:32</t>
+  </si>
+  <si>
+    <t>11/29/2025</t>
+  </si>
+  <si>
+    <t>UCR_S004_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>sleep diary</t>
+  </si>
+  <si>
+    <t>6/26/2025 5:30</t>
+  </si>
+  <si>
+    <t>6/25/2025 22:00</t>
+  </si>
+  <si>
+    <t>implausible value, changed to sleep_v2</t>
+  </si>
+  <si>
+    <t>6/30/2025 22:45</t>
+  </si>
+  <si>
+    <t>6/29/2025 22:45</t>
+  </si>
+  <si>
+    <t>6/30/2025 23:00</t>
+  </si>
+  <si>
+    <t>6/29/2025 23:00</t>
+  </si>
+  <si>
+    <t>UCR_S005_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>6/23/2025 23:59</t>
+  </si>
+  <si>
+    <t>6/23/2025 23:35</t>
+  </si>
+  <si>
+    <t>implausible value, changed to bedtime_v2</t>
+  </si>
+  <si>
+    <t>6/28/2025 11:40</t>
+  </si>
+  <si>
+    <t>6/27/2025 23:40</t>
+  </si>
+  <si>
+    <t>6/28/2025 7:20</t>
+  </si>
+  <si>
+    <t>6/28/2025 7:11</t>
+  </si>
+  <si>
+    <t>implausible value, changed to out_ofbed_v2</t>
+  </si>
+  <si>
+    <t>implausible value, changed to offset_v2</t>
+  </si>
+  <si>
+    <t>UCR_S007_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S011_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S012_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/13/2025 22:46</t>
+  </si>
+  <si>
+    <t>7/13/2025 10:36</t>
+  </si>
+  <si>
+    <t>UCR_S013_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/13/2025 23:30</t>
+  </si>
+  <si>
+    <t>UCR_S014_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/18/2025 4:56</t>
+  </si>
+  <si>
+    <t>7/17/2025 21:00</t>
+  </si>
+  <si>
+    <t>UCR_S016_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/19/2025 23:30</t>
+  </si>
+  <si>
+    <t>7/18/2025 23:30</t>
+  </si>
+  <si>
+    <t>UCR_S018_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/21/2025 5:18</t>
+  </si>
+  <si>
+    <t>7/20/2025 22:15</t>
+  </si>
+  <si>
+    <t>7/23/2025 5:16</t>
+  </si>
+  <si>
+    <t>7/22/2025 22:30</t>
+  </si>
+  <si>
+    <t>7/25/2025 5:20</t>
+  </si>
+  <si>
+    <t>7/25/2025 2:30</t>
+  </si>
+  <si>
+    <t>UCR_S019_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/24/2025 6:47</t>
+  </si>
+  <si>
+    <t>7/23/2025 23:00</t>
+  </si>
+  <si>
+    <t>7/26/2025 12:01</t>
+  </si>
+  <si>
+    <t>7/25/2025 00:01</t>
+  </si>
+  <si>
+    <t>7/27/2025 9:26</t>
+  </si>
+  <si>
+    <t>7/26/2025 23:02</t>
+  </si>
+  <si>
+    <t>7/28/2025 9:12</t>
+  </si>
+  <si>
+    <t>7/27/2025 23:13</t>
+  </si>
+  <si>
+    <t>UCR_S020_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>7/25/2025 23:40</t>
+  </si>
+  <si>
+    <t>7/24/2025 23:40</t>
+  </si>
+  <si>
+    <t>UCR_S022_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S023_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S025_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S026_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S027_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S028_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>8/16/2025 22:15</t>
+  </si>
+  <si>
+    <t>8/15/2025 22:15</t>
+  </si>
+  <si>
+    <t>8/16/2025 23:05</t>
+  </si>
+  <si>
+    <t>8/15/2025 23:05</t>
+  </si>
+  <si>
+    <t>UCR_S029_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>8/13/2025 22:00</t>
+  </si>
+  <si>
+    <t>8/13/2025 22:45</t>
+  </si>
+  <si>
+    <t>8/16/2025 0:19</t>
+  </si>
+  <si>
+    <t>8/17/2025 0:19</t>
+  </si>
+  <si>
+    <t>8/18/2025 22:00</t>
+  </si>
+  <si>
+    <t>8/17/2025 22:00</t>
+  </si>
+  <si>
+    <t>UCR_S031_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S033_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S034_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S036_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S037_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S038_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S039_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>UCR_S040_SLEEPDIARY_202509</t>
+  </si>
+  <si>
+    <t>6/26/2025 11:30</t>
+  </si>
+  <si>
+    <t>6/26/2025 11:55</t>
+  </si>
+  <si>
+    <t>6/26/2025 23:30</t>
+  </si>
+  <si>
+    <t>6/26/2025 23:55</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -148,6 +391,24 @@
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,10 +431,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -508,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3538B33B-749F-0E43-A226-AA8FBD28EB7C}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="30.6640625" customWidth="1"/>
@@ -519,211 +793,2603 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+      <c r="A2" s="2">
         <v>45940</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+      <c r="A3" s="2">
         <v>45940</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>45940</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="A5" s="2">
         <v>45940</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="A6" s="2">
         <v>45940</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>5</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="A7" s="2">
         <v>45940</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>7</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="A8" s="2">
         <v>45940</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>7</v>
       </c>
-      <c r="E8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="6">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="6">
+        <v>6</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6">
+        <v>6</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="6">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="6">
+        <v>6</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="6">
+        <v>6</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="7">
+        <v>45839</v>
+      </c>
+      <c r="G19" s="7">
+        <v>45840</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="9">
+        <v>45843.489583333336</v>
+      </c>
+      <c r="G20" s="9">
+        <v>45843.989583333336</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="7">
+        <v>45846.958333333336</v>
+      </c>
+      <c r="G21" s="7">
+        <v>45845.958333333336</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="7">
+        <v>45846.979166666664</v>
+      </c>
+      <c r="G22" s="7">
+        <v>45845.979166666664</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="6">
+        <v>5</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="7">
+        <v>45850.430555555555</v>
+      </c>
+      <c r="G23" s="7">
+        <v>45849.930555555555</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="7">
+        <v>45846.260416666664</v>
+      </c>
+      <c r="G24" s="7">
+        <v>45845.989583333336</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="7">
+        <v>45847.95</v>
+      </c>
+      <c r="G25" s="7">
+        <v>45846.958333333336</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="6">
+        <v>3</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="7">
+        <v>45848.270138888889</v>
+      </c>
+      <c r="G26" s="7">
+        <v>45847.978472222225</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="7">
+        <v>45848.496527777781</v>
+      </c>
+      <c r="G27" s="7">
+        <v>45848.999305555553</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="7">
+        <v>45850.986111111109</v>
+      </c>
+      <c r="G28" s="7">
+        <v>45850.979166666664</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="7">
+        <v>45850.979166666664</v>
+      </c>
+      <c r="G29" s="7">
+        <v>45850.986111111109</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="6">
+        <v>7</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="7">
+        <v>45852.948611111111</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="7">
+        <v>45845.239583333336</v>
+      </c>
+      <c r="G32" s="7">
+        <v>45846.239583333336</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="6">
+        <v>2</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="7">
+        <v>45846.461805555555</v>
+      </c>
+      <c r="G33" s="7">
+        <v>45846.961805555555</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="6">
+        <v>3</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="7">
+        <v>45847.46875</v>
+      </c>
+      <c r="G34" s="7">
+        <v>45847.96875</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="6">
+        <v>5</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="7">
+        <v>45849.479166666664</v>
+      </c>
+      <c r="G35" s="7">
+        <v>45849.979166666664</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="6">
+        <v>6</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="7">
+        <v>45851.479166666664</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" s="6">
+        <v>4</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="6">
+        <v>5</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="6">
+        <v>3</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" s="6">
+        <v>5</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="6">
+        <v>3</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D43" s="6">
+        <v>4</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="6">
+        <v>6</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D45" s="6">
+        <v>7</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="6">
+        <v>4</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="6">
+        <v>7</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="7">
+        <v>45872</v>
+      </c>
+      <c r="G47" s="7">
+        <v>45873</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D48" s="6">
+        <v>7</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="7">
+        <v>45873.895833333336</v>
+      </c>
+      <c r="G48" s="7">
+        <v>45872.895833333336</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="6">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="7">
+        <v>45874.314583333333</v>
+      </c>
+      <c r="G49" s="7">
+        <v>45873.986111111109</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D50" s="6">
+        <v>2</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F50" s="7">
+        <v>45875.979166666664</v>
+      </c>
+      <c r="G50" s="7">
+        <v>45874.979166666664</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D51" s="6">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" s="7">
+        <v>45875.993055555555</v>
+      </c>
+      <c r="G51" s="7">
+        <v>45874.993055555555</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="6">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="7">
+        <v>45876.3125</v>
+      </c>
+      <c r="G52" s="7">
+        <v>45875.3125</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="7">
+        <v>45876.318055555559</v>
+      </c>
+      <c r="G53" s="7">
+        <v>45875.318055555559</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F54" s="7">
+        <v>45875.270833333336</v>
+      </c>
+      <c r="G54" s="7">
+        <v>45875.993055555555</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="6">
+        <v>3</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" s="7">
+        <v>45874.993055555555</v>
+      </c>
+      <c r="G55" s="7">
+        <v>45875.993055555555</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="6">
+        <v>3</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="7">
+        <v>45875.270833333336</v>
+      </c>
+      <c r="G56" s="7">
+        <v>45876.270833333336</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" s="6">
+        <v>3</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="7">
+        <v>45875.270833333336</v>
+      </c>
+      <c r="G57" s="7">
+        <v>45876.270833333336</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="6">
+        <v>5</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="7">
+        <v>45878.548611111109</v>
+      </c>
+      <c r="G58" s="7">
+        <v>45878.048611111109</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="6">
+        <v>5</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="7">
+        <v>45878.548611111109</v>
+      </c>
+      <c r="G59" s="7">
+        <v>45878.048611111109</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="6">
+        <v>4</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="7">
+        <v>45877.169444444444</v>
+      </c>
+      <c r="G60" s="7">
+        <v>45876.919444444444</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D61" s="6">
+        <v>3</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="7">
+        <v>45876.986111111109</v>
+      </c>
+      <c r="G61" s="7">
+        <v>45875.986111111109</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D62" s="6">
+        <v>3</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F62" s="7">
+        <v>45876.993055555555</v>
+      </c>
+      <c r="G62" s="7">
+        <v>45875.993055555555</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="6">
+        <v>5</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="7">
+        <v>45879.003472222219</v>
+      </c>
+      <c r="G63" s="7">
+        <v>45878.003472222219</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" s="6">
+        <v>5</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F64" s="7">
+        <v>45879.003472222219</v>
+      </c>
+      <c r="G64" s="7">
+        <v>45878.003472222219</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="6">
+        <v>5</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="7">
+        <v>45879.3125</v>
+      </c>
+      <c r="G65" s="7">
+        <v>45878.3125</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66" s="6">
+        <v>5</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F66" s="7">
+        <v>45879.336805555555</v>
+      </c>
+      <c r="G66" s="7">
+        <v>45878.336805555555</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="6">
+        <v>6</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="7">
+        <v>45878.072916666664</v>
+      </c>
+      <c r="G67" s="7">
+        <v>45879.072916666664</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="6">
+        <v>6</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="7">
+        <v>45878.090277777781</v>
+      </c>
+      <c r="G68" s="7">
+        <v>45879.090277777781</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D69" s="6">
+        <v>6</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="7">
+        <v>45878.291666666664</v>
+      </c>
+      <c r="G69" s="7">
+        <v>45879.291666666664</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70" s="6">
+        <v>6</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" s="7">
+        <v>45878.3125</v>
+      </c>
+      <c r="G70" s="7">
+        <v>45879.3125</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="7">
+        <v>45881.958333333336</v>
+      </c>
+      <c r="G71" s="7">
+        <v>45880.958333333336</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D72" s="6">
+        <v>5</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D73" s="6">
+        <v>5</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D74" s="6">
+        <v>2</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G74" s="7">
+        <v>45881.916666666664</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="6">
+        <v>2</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="7">
+        <v>45881.947916666664</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D76" s="6">
+        <v>6</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="6">
+        <v>7</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D78" s="6">
+        <v>3</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="7">
+        <v>45889.395833333336</v>
+      </c>
+      <c r="G78" s="7">
+        <v>45889.895833333336</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D79" s="6">
+        <v>1</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="7">
+        <v>45888.198611111111</v>
+      </c>
+      <c r="G79" s="7">
+        <v>45887.958333333336</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D80" s="6">
+        <v>2</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="7">
+        <v>45889.361111111109</v>
+      </c>
+      <c r="G80" s="7">
+        <v>45889.041666666664</v>
+      </c>
+      <c r="H80" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D81" s="6">
+        <v>1</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="7">
+        <v>45894.30972222222</v>
+      </c>
+      <c r="G81" s="7">
+        <v>45894.930555555555</v>
+      </c>
+      <c r="H81" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" s="6">
+        <v>5</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F82" s="7">
+        <v>45898.255555555559</v>
+      </c>
+      <c r="G82" s="7">
+        <v>45899.255555555559</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D83" s="6">
+        <v>6</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F83" s="7">
+        <v>45899.355555555558</v>
+      </c>
+      <c r="G83" s="7">
+        <v>45899.355555555558</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="6">
+        <v>7</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84" s="7">
+        <v>45930.929166666669</v>
+      </c>
+      <c r="G84" s="7">
+        <v>45900.429166666669</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D85" s="6">
+        <v>3</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="7">
+        <v>45897.03125</v>
+      </c>
+      <c r="G85" s="7">
+        <v>45898.03125</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D86" s="6">
+        <v>4</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F86" s="7">
+        <v>45898.020833333336</v>
+      </c>
+      <c r="G86" s="7">
+        <v>45899.020833333336</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D87" s="6">
+        <v>5</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="7">
+        <v>45899.487500000003</v>
+      </c>
+      <c r="G87" s="7">
+        <v>45899.908333333333</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="6">
+        <v>1</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="7">
+        <v>45896.302083333336</v>
+      </c>
+      <c r="G88" s="7">
+        <v>45896.020833333336</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="6">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F89" s="7">
+        <v>45896.520833333336</v>
+      </c>
+      <c r="G89" s="7">
+        <v>45896.020833333336</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D90" s="6">
+        <v>3</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="7">
+        <v>45898.1875</v>
+      </c>
+      <c r="G90" s="7">
+        <v>45897.979166666664</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D91" s="6">
+        <v>3</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="7">
+        <v>45898.979166666664</v>
+      </c>
+      <c r="G91" s="7">
+        <v>45897.979166666664</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="6">
+        <v>4</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="7">
+        <v>45899.364583333336</v>
+      </c>
+      <c r="G92" s="7">
+        <v>45899.020833333336</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="6">
+        <v>5</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="7">
+        <v>45900.058333333334</v>
+      </c>
+      <c r="G93" s="7">
+        <v>45900.048611111109</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D94" s="6">
+        <v>5</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F94" s="7">
+        <v>45900.048611111109</v>
+      </c>
+      <c r="G94" s="7">
+        <v>45900.058333333334</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D95" s="6">
+        <v>6</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="7">
+        <v>45902.247916666667</v>
+      </c>
+      <c r="G95" s="7">
+        <v>45901.958333333336</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D96" s="6">
+        <v>6</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F96" s="7">
+        <v>45902.958333333336</v>
+      </c>
+      <c r="G96" s="7">
+        <v>45901.958333333336</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="6">
+        <v>1</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" s="7">
+        <v>45896.982638888891</v>
+      </c>
+      <c r="G97" s="7">
+        <v>45895.982638888891</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D98" s="6">
+        <v>5</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="7">
+        <v>45899.53125</v>
+      </c>
+      <c r="G98" s="7">
+        <v>45900.03125</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D99" s="6">
+        <v>5</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F99" s="7">
+        <v>45900.53125</v>
+      </c>
+      <c r="G99" s="7">
+        <v>45900.03125</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D100" s="6">
+        <v>2</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="7">
+        <v>45902.211805555555</v>
+      </c>
+      <c r="G100" s="7">
+        <v>45901.958333333336</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
